--- a/cases/orbit_catalog.xlsx
+++ b/cases/orbit_catalog.xlsx
@@ -663,7 +663,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="18.75"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -742,7 +742,32 @@
           <t>illumination_condition</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>orbit_period_s</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>eclipse_entry_time_s</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>eclipse_exit_time_s</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>eclipse_duration_s</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>sunlit_duration_s</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -793,7 +818,7 @@
           <t>full_sun</t>
         </is>
       </c>
-      <c r="M2" s="8" t="n"/>
+      <c r="R2" s="8" t="n"/>
     </row>
     <row r="3" ht="43.5" customHeight="1" thickBot="1">
       <c r="A3" s="9" t="n">
@@ -840,7 +865,7 @@
           <t>full_sun</t>
         </is>
       </c>
-      <c r="M3" s="13" t="n"/>
+      <c r="R3" s="13" t="n"/>
     </row>
     <row r="4" ht="43.5" customHeight="1" thickBot="1">
       <c r="A4" s="4" t="n">
@@ -887,7 +912,7 @@
           <t>full_sun</t>
         </is>
       </c>
-      <c r="M4" s="8" t="n"/>
+      <c r="R4" s="8" t="n"/>
     </row>
     <row r="5" ht="29.25" customHeight="1" thickBot="1">
       <c r="A5" s="9" t="n">
@@ -934,7 +959,7 @@
           <t>full_sun</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
+      <c r="R5" s="13" t="n"/>
     </row>
     <row r="6" ht="43.5" customHeight="1" thickBot="1">
       <c r="A6" s="4" t="n">
@@ -981,7 +1006,7 @@
           <t>full_sun</t>
         </is>
       </c>
-      <c r="M6" s="8" t="n"/>
+      <c r="R6" s="8" t="n"/>
     </row>
     <row r="7" ht="43.5" customHeight="1" thickBot="1">
       <c r="A7" s="9" t="n">
@@ -1028,7 +1053,7 @@
           <t>full_sun</t>
         </is>
       </c>
-      <c r="M7" s="13" t="n"/>
+      <c r="R7" s="13" t="n"/>
     </row>
     <row r="8" ht="43.5" customHeight="1" thickBot="1">
       <c r="A8" s="4" t="n">
@@ -1073,7 +1098,7 @@
           <t>eclipse</t>
         </is>
       </c>
-      <c r="M8" s="15" t="inlineStr">
+      <c r="R8" s="15" t="inlineStr">
         <is>
           <t>calculated_by_stk</t>
         </is>
@@ -1122,7 +1147,7 @@
           <t>eclipse</t>
         </is>
       </c>
-      <c r="M9" s="17" t="inlineStr">
+      <c r="R9" s="17" t="inlineStr">
         <is>
           <t>calculated_by_stk</t>
         </is>
@@ -1171,7 +1196,7 @@
           <t>eclipse</t>
         </is>
       </c>
-      <c r="M10" s="15" t="inlineStr">
+      <c r="R10" s="15" t="inlineStr">
         <is>
           <t>calculated_by_stk</t>
         </is>
@@ -1222,7 +1247,7 @@
           <t>full_sun</t>
         </is>
       </c>
-      <c r="M11" s="13" t="n"/>
+      <c r="R11" s="13" t="n"/>
     </row>
     <row r="12" ht="43.5" customHeight="1" thickBot="1">
       <c r="A12" s="4" t="n">
@@ -1267,7 +1292,7 @@
           <t>eclipse</t>
         </is>
       </c>
-      <c r="M12" s="15" t="inlineStr">
+      <c r="R12" s="15" t="inlineStr">
         <is>
           <t>calculated_by_stk</t>
         </is>
@@ -1316,7 +1341,7 @@
           <t>eclipse</t>
         </is>
       </c>
-      <c r="M13" s="17" t="inlineStr">
+      <c r="R13" s="17" t="inlineStr">
         <is>
           <t>calculated_by_stk</t>
         </is>
@@ -1367,7 +1392,7 @@
           <t>eclipse_noon_midnight</t>
         </is>
       </c>
-      <c r="M14" s="8" t="n"/>
+      <c r="R14" s="8" t="n"/>
     </row>
     <row r="15" ht="60.75" customHeight="1" thickBot="1">
       <c r="A15" s="18" t="n">
@@ -1414,7 +1439,7 @@
           <t>full_sun</t>
         </is>
       </c>
-      <c r="M15" s="13" t="inlineStr">
+      <c r="R15" s="13" t="inlineStr">
         <is>
           <t>tumbling_free_motion</t>
         </is>
@@ -1465,7 +1490,7 @@
           <t>full_sun</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="R16" s="8" t="inlineStr">
         <is>
           <t>tumbling_free_motion</t>
         </is>
@@ -1514,7 +1539,7 @@
           <t>eclipse</t>
         </is>
       </c>
-      <c r="M17" s="13" t="inlineStr">
+      <c r="R17" s="13" t="inlineStr">
         <is>
           <t>tumbling_free_motion</t>
         </is>
@@ -1563,7 +1588,7 @@
           <t>eclipse</t>
         </is>
       </c>
-      <c r="M18" s="8" t="inlineStr">
+      <c r="R18" s="8" t="inlineStr">
         <is>
           <t>tumbling_free_motion</t>
         </is>
@@ -1612,7 +1637,7 @@
           <t>eclipse</t>
         </is>
       </c>
-      <c r="M19" s="13" t="inlineStr">
+      <c r="R19" s="13" t="inlineStr">
         <is>
           <t>tumbling_free_motion</t>
         </is>
@@ -1661,7 +1686,7 @@
           <t>eclipse</t>
         </is>
       </c>
-      <c r="M20" s="8" t="inlineStr">
+      <c r="R20" s="8" t="inlineStr">
         <is>
           <t>tumbling_free_motion</t>
         </is>
@@ -1712,7 +1737,7 @@
           <t>eclipse_noon_midnight</t>
         </is>
       </c>
-      <c r="M21" s="23" t="inlineStr">
+      <c r="R21" s="23" t="inlineStr">
         <is>
           <t>tumbling_free_motion</t>
         </is>
